--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2017/DISTRICT_OF_COLUMBIA_2017.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2017/DISTRICT_OF_COLUMBIA_2017.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -477,7 +492,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C8">
@@ -488,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -501,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C10">
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -579,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Salto de Agua</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C16">
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Socoltenango</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Múzquiz</t>
@@ -706,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -721,7 +811,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -789,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -802,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -815,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -828,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -841,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -854,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -885,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -900,7 +1045,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -955,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Timilpan</t>
@@ -968,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -981,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -1007,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1038,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jaral del Progreso</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C49">
@@ -1051,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>León</t>
@@ -1064,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -1077,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1097,7 +1302,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C53">
@@ -1108,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1121,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alcozauca de Guerrero</t>
+          <t>Alcozauca De Guerrero</t>
         </is>
       </c>
       <c r="C55">
@@ -1134,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -1147,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C57">
@@ -1160,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C58">
@@ -1173,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C59">
@@ -1186,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1199,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C61">
@@ -1212,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -1225,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -1238,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -1251,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -1264,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -1277,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Tlalchapa</t>
@@ -1290,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C68">
@@ -1303,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -1316,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1347,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C72">
@@ -1360,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1373,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C74">
@@ -1386,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -1399,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1430,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C78">
@@ -1443,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Sayula</t>
@@ -1456,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1487,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -1500,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -1513,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C84">
@@ -1526,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1557,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C87">
@@ -1570,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -1583,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1614,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1645,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Chahuites</t>
@@ -1658,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C94">
@@ -1671,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C95">
@@ -1684,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C96">
@@ -1697,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C97">
@@ -1710,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C98">
@@ -1723,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C99">
@@ -1736,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>San Carlos Yautepec</t>
@@ -1749,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>San Jerónimo Taviche</t>
@@ -1762,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>San Juan Bautista Cuicatlán</t>
@@ -1775,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>San Juan Guelavía</t>
@@ -1788,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>San Juan Guichicovi</t>
@@ -1801,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -1814,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>San Miguel Tequixtepec</t>
@@ -1827,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -1840,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -1853,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Santa Inés del Monte</t>
+          <t>Santa Inés Del Monte</t>
         </is>
       </c>
       <c r="C109">
@@ -1866,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Santa María Huazolotitlán</t>
@@ -1879,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Santo Domingo Teojomulco</t>
@@ -1892,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Villa Díaz Ordaz</t>
@@ -1905,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1936,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -1949,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Aljojuca</t>
@@ -1962,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Amozoc</t>
@@ -1975,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -1988,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Atzala</t>
@@ -2001,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Atzitzihuacán</t>
@@ -2014,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -2027,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -2040,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C123">
@@ -2053,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C124">
@@ -2066,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2079,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -2092,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Santa Inés Ahuatempan</t>
@@ -2105,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Santa Isabel Cholula</t>
@@ -2118,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Soltepec</t>
@@ -2131,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -2144,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -2157,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C132">
@@ -2170,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C133">
@@ -2183,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C134">
@@ -2196,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Tlapanalá</t>
@@ -2209,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -2222,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Xayacatlán de Bravo</t>
+          <t>Xayacatlán De Bravo</t>
         </is>
       </c>
       <c r="C137">
@@ -2235,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -2248,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2268,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C140">
@@ -2279,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -2292,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2323,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -2336,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2367,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -2380,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2411,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -2424,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2455,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -2468,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -2481,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -2494,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2525,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -2538,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -2551,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>San Pablo del Monte</t>
+          <t>San Pablo Del Monte</t>
         </is>
       </c>
       <c r="C160">
@@ -2564,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2584,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C162">
@@ -2595,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -2608,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -2621,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2634,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Cuichapa</t>
@@ -2647,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -2660,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -2673,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C169">
@@ -2686,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -2699,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -2712,9 +3437,14 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C172">
@@ -2725,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -2738,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -2751,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2764,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -2777,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -2790,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2813,76 +3573,6 @@
       </c>
       <c r="D179">
         <v>1</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 826,856</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Junio de 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
